--- a/artfynd/A 29506-2026 artfynd.xlsx
+++ b/artfynd/A 29506-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137452676</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137452681</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137452679</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137452682</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137452675</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>137452680</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
